--- a/Templates/water-quality-analysis/Test_code/SSEMG_IS_20260224_label-table.xlsx
+++ b/Templates/water-quality-analysis/Test_code/SSEMG_IS_20260224_label-table.xlsx
@@ -17,9 +17,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd HH:mm:ss UTC"/>
-  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -57,12 +54,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -385,7 +381,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SSEMG_R0019</t>
+          <t>SSEMG_R0027</t>
         </is>
       </c>
       <c r="C2">
@@ -400,7 +396,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SSEMG_R0016</t>
+          <t>SSEMG_R0019</t>
         </is>
       </c>
       <c r="C3">
@@ -415,7 +411,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SSEMG_R0030</t>
+          <t>SSEMG_R0047</t>
         </is>
       </c>
       <c r="C4">
@@ -430,7 +426,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SSEMG_R0001</t>
+          <t>SSEMG_R0003</t>
         </is>
       </c>
       <c r="C5">
@@ -445,7 +441,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SSEMG_R0025</t>
+          <t>SSEMG_R0002</t>
         </is>
       </c>
       <c r="C6">
@@ -460,7 +456,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SSEMG_R0024</t>
+          <t>SSEMG_R0035</t>
         </is>
       </c>
       <c r="C7">
@@ -475,7 +471,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SSEMG_R0012</t>
+          <t>SSEMG_R0042</t>
         </is>
       </c>
       <c r="C8">
@@ -490,7 +486,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SSEMG_R0003</t>
+          <t>SSEMG_R0046</t>
         </is>
       </c>
       <c r="C9">
@@ -505,7 +501,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SSEMG_R0040</t>
+          <t>SSEMG_R0026</t>
         </is>
       </c>
       <c r="C10">
@@ -520,7 +516,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SSEMG_R0013</t>
+          <t>SSEMG_R0006</t>
         </is>
       </c>
       <c r="C11">
@@ -535,7 +531,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SSEMG_R0041</t>
+          <t>SSEMG_R0017</t>
         </is>
       </c>
       <c r="C12">
@@ -550,7 +546,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SSEMG_R0033</t>
+          <t>SSEMG_R0040</t>
         </is>
       </c>
       <c r="C13">
@@ -565,7 +561,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SSEMG_R0021</t>
+          <t>SSEMG_R0023</t>
         </is>
       </c>
       <c r="C14">
@@ -580,7 +576,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SSEMG_R0046</t>
+          <t>SSEMG_R0020</t>
         </is>
       </c>
       <c r="C15">
@@ -595,7 +591,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SSEMG_R0022</t>
+          <t>SSEMG_R0024</t>
         </is>
       </c>
       <c r="C16">
@@ -610,7 +606,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SSEMG_R0004</t>
+          <t>SSEMG_R0010</t>
         </is>
       </c>
       <c r="C17">
@@ -625,7 +621,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SSEMG_R0020</t>
+          <t>SSEMG_R0041</t>
         </is>
       </c>
       <c r="C18">
@@ -640,7 +636,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SSEMG_R0005</t>
+          <t>SSEMG_R0045</t>
         </is>
       </c>
       <c r="C19">
@@ -655,7 +651,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SSEMG_R0042</t>
+          <t>SSEMG_R0031</t>
         </is>
       </c>
       <c r="C20">
@@ -670,7 +666,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SSEMG_R0045</t>
+          <t>SSEMG_R0012</t>
         </is>
       </c>
       <c r="C21">
@@ -685,7 +681,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SSEMG_R0018</t>
+          <t>SSEMG_R0048</t>
         </is>
       </c>
       <c r="C22">
@@ -700,7 +696,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SSEMG_R0034</t>
+          <t>SSEMG_R0043</t>
         </is>
       </c>
       <c r="C23">
@@ -715,7 +711,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SSEMG_R0044</t>
+          <t>SSEMG_R0016</t>
         </is>
       </c>
       <c r="C24">
@@ -730,7 +726,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SSEMG_R0023</t>
+          <t>SSEMG_R0030</t>
         </is>
       </c>
       <c r="C25">
@@ -745,7 +741,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SSEMG_R0037</t>
+          <t>SSEMG_R0011</t>
         </is>
       </c>
       <c r="C26">
@@ -760,7 +756,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SSEMG_R0027</t>
+          <t>SSEMG_R0032</t>
         </is>
       </c>
       <c r="C27">
@@ -775,7 +771,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SSEMG_R0010</t>
+          <t>SSEMG_R0005</t>
         </is>
       </c>
       <c r="C28">
@@ -790,7 +786,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SSEMG_R0029</t>
+          <t>SSEMG_R0028</t>
         </is>
       </c>
       <c r="C29">
@@ -805,7 +801,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SSEMG_R0006</t>
+          <t>SSEMG_R0025</t>
         </is>
       </c>
       <c r="C30">
@@ -820,7 +816,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SSEMG_R0031</t>
+          <t>SSEMG_R0034</t>
         </is>
       </c>
       <c r="C31">
@@ -835,7 +831,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SSEMG_R0043</t>
+          <t>SSEMG_R0038</t>
         </is>
       </c>
       <c r="C32">
@@ -850,7 +846,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SSEMG_R0008</t>
+          <t>SSEMG_R0029</t>
         </is>
       </c>
       <c r="C33">
@@ -865,7 +861,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SSEMG_R0032</t>
+          <t>SSEMG_R0008</t>
         </is>
       </c>
       <c r="C34">
@@ -880,7 +876,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SSEMG_R0028</t>
+          <t>SSEMG_R0044</t>
         </is>
       </c>
       <c r="C35">
@@ -895,7 +891,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SSEMG_R0036</t>
+          <t>SSEMG_R0022</t>
         </is>
       </c>
       <c r="C36">
@@ -910,7 +906,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SSEMG_R0007</t>
+          <t>SSEMG_R0021</t>
         </is>
       </c>
       <c r="C37">
@@ -925,7 +921,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SSEMG_R0017</t>
+          <t>SSEMG_R0036</t>
         </is>
       </c>
       <c r="C38">
@@ -940,7 +936,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SSEMG_R0014</t>
+          <t>SSEMG_R0001</t>
         </is>
       </c>
       <c r="C39">
@@ -955,7 +951,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SSEMG_R0038</t>
+          <t>SSEMG_R0009</t>
         </is>
       </c>
       <c r="C40">
@@ -970,7 +966,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SSEMG_R0039</t>
+          <t>SSEMG_R0007</t>
         </is>
       </c>
       <c r="C41">
@@ -985,7 +981,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SSEMG_R0026</t>
+          <t>SSEMG_R0018</t>
         </is>
       </c>
       <c r="C42">
@@ -1000,7 +996,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SSEMG_R0048</t>
+          <t>SSEMG_R0037</t>
         </is>
       </c>
       <c r="C43">
@@ -1015,7 +1011,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SSEMG_R0009</t>
+          <t>SSEMG_R0033</t>
         </is>
       </c>
       <c r="C44">
@@ -1030,7 +1026,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SSEMG_R0011</t>
+          <t>SSEMG_R0004</t>
         </is>
       </c>
       <c r="C45">
@@ -1045,7 +1041,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SSEMG_R0035</t>
+          <t>SSEMG_R0014</t>
         </is>
       </c>
       <c r="C46">
@@ -1060,7 +1056,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SSEMG_R0002</t>
+          <t>SSEMG_R0013</t>
         </is>
       </c>
       <c r="C47">
@@ -1075,7 +1071,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SSEMG_R0047</t>
+          <t>SSEMG_R0039</t>
         </is>
       </c>
       <c r="C48">
@@ -1127,7 +1123,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602232100_AQ</t>
+          <t>SSEMG_COA_IS_202602241900_AQ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1144,7 +1140,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602232100_NU</t>
+          <t>SSEMG_COA_IS_202602241900_NU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1161,7 +1157,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602232100_EX</t>
+          <t>SSEMG_COA_IS_202602241900_EX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1178,7 +1174,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602232100_LV</t>
+          <t>SSEMG_COA_IS_202602241900_LV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1195,7 +1191,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602251100_AQ</t>
+          <t>SSEMG_STA_IS_202602232300_AQ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1212,7 +1208,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602251100_NU</t>
+          <t>SSEMG_STA_IS_202602232300_NU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1229,7 +1225,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602251100_EX</t>
+          <t>SSEMG_STA_IS_202602232300_EX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1246,7 +1242,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602251100_LV</t>
+          <t>SSEMG_STA_IS_202602232300_LV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1263,7 +1259,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240500_AQ</t>
+          <t>SSEMG_STA_IS_202602232100_AQ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1280,7 +1276,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240500_NU</t>
+          <t>SSEMG_STA_IS_202602232100_NU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1297,7 +1293,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240500_EX</t>
+          <t>SSEMG_STA_IS_202602232100_EX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1314,7 +1310,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240500_LV</t>
+          <t>SSEMG_STA_IS_202602232100_LV</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1331,7 +1327,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602242100_AQ</t>
+          <t>SSEMG_COA_IS_202602250700_AQ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1348,7 +1344,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602242100_NU</t>
+          <t>SSEMG_COA_IS_202602250700_NU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1365,7 +1361,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602242100_EX</t>
+          <t>SSEMG_COA_IS_202602250700_EX</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1382,7 +1378,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602242100_LV</t>
+          <t>SSEMG_COA_IS_202602250700_LV</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1399,7 +1395,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250100_AQ</t>
+          <t>SSEMG_COA_IS_202602232100_AQ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1416,7 +1412,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250100_NU</t>
+          <t>SSEMG_COA_IS_202602232100_NU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1433,7 +1429,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250100_EX</t>
+          <t>SSEMG_COA_IS_202602232100_EX</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1450,7 +1446,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250100_LV</t>
+          <t>SSEMG_COA_IS_202602232100_LV</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1467,7 +1463,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240100_AQ</t>
+          <t>SSEMG_STA_IS_202602240900_AQ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1484,7 +1480,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240100_NU</t>
+          <t>SSEMG_STA_IS_202602240900_NU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1501,7 +1497,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240100_EX</t>
+          <t>SSEMG_STA_IS_202602240900_EX</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1518,7 +1514,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240100_LV</t>
+          <t>SSEMG_STA_IS_202602240900_LV</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1535,7 +1531,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241500_AQ</t>
+          <t>SSEMG_COA_IS_202602242300_AQ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1552,7 +1548,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241500_NU</t>
+          <t>SSEMG_COA_IS_202602242300_NU</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1569,7 +1565,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241500_EX</t>
+          <t>SSEMG_COA_IS_202602242300_EX</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1586,7 +1582,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241500_LV</t>
+          <t>SSEMG_COA_IS_202602242300_LV</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1603,7 +1599,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240700_AQ</t>
+          <t>SSEMG_COA_IS_202602240900_AQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1620,7 +1616,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240700_NU</t>
+          <t>SSEMG_COA_IS_202602240900_NU</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1637,7 +1633,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240700_EX</t>
+          <t>SSEMG_COA_IS_202602240900_EX</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1654,7 +1650,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240700_LV</t>
+          <t>SSEMG_COA_IS_202602240900_LV</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1671,7 +1667,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250500_AQ</t>
+          <t>SSEMG_COA_IS_202602242100_AQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1688,7 +1684,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250500_NU</t>
+          <t>SSEMG_COA_IS_202602242100_NU</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1705,7 +1701,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250500_EX</t>
+          <t>SSEMG_COA_IS_202602242100_EX</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1722,7 +1718,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250500_LV</t>
+          <t>SSEMG_COA_IS_202602242100_LV</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1739,7 +1735,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602232100_AQ</t>
+          <t>SSEMG_STA_IS_202602242100_AQ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1756,7 +1752,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602232100_NU</t>
+          <t>SSEMG_STA_IS_202602242100_NU</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1773,7 +1769,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602232100_EX</t>
+          <t>SSEMG_STA_IS_202602242100_EX</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1790,7 +1786,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602232100_LV</t>
+          <t>SSEMG_STA_IS_202602242100_LV</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1807,7 +1803,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250700_AQ</t>
+          <t>SSEMG_COA_IS_202602231700_AQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1824,7 +1820,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250700_NU</t>
+          <t>SSEMG_COA_IS_202602231700_NU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1841,7 +1837,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250700_EX</t>
+          <t>SSEMG_COA_IS_202602231700_EX</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1858,7 +1854,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250700_LV</t>
+          <t>SSEMG_COA_IS_202602231700_LV</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1875,7 +1871,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240300_AQ</t>
+          <t>SSEMG_STA_IS_202602250500_AQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1892,7 +1888,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240300_NU</t>
+          <t>SSEMG_STA_IS_202602250500_NU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1909,7 +1905,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240300_EX</t>
+          <t>SSEMG_STA_IS_202602250500_EX</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1926,7 +1922,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240300_LV</t>
+          <t>SSEMG_STA_IS_202602250500_LV</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1943,7 +1939,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240900_AQ</t>
+          <t>SSEMG_COA_IS_202602251100_AQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1960,7 +1956,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240900_NU</t>
+          <t>SSEMG_COA_IS_202602251100_NU</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1977,7 +1973,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240900_EX</t>
+          <t>SSEMG_COA_IS_202602251100_EX</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1994,7 +1990,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240900_LV</t>
+          <t>SSEMG_COA_IS_202602251100_LV</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2011,7 +2007,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241900_AQ</t>
+          <t>SSEMG_COA_IS_202602250900_AQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2028,7 +2024,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241900_NU</t>
+          <t>SSEMG_COA_IS_202602250900_NU</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2045,7 +2041,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241900_EX</t>
+          <t>SSEMG_COA_IS_202602250900_EX</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2062,7 +2058,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241900_LV</t>
+          <t>SSEMG_COA_IS_202602250900_LV</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2147,7 +2143,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231700_AQ</t>
+          <t>SSEMG_STA_IS_202602251100_AQ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2164,7 +2160,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231700_NU</t>
+          <t>SSEMG_STA_IS_202602251100_NU</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2181,7 +2177,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231700_EX</t>
+          <t>SSEMG_STA_IS_202602251100_EX</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2198,7 +2194,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231700_LV</t>
+          <t>SSEMG_STA_IS_202602251100_LV</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2215,7 +2211,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241700_AQ</t>
+          <t>SSEMG_STA_IS_202602241100_AQ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2232,7 +2228,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241700_NU</t>
+          <t>SSEMG_STA_IS_202602241100_NU</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2249,7 +2245,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241700_EX</t>
+          <t>SSEMG_STA_IS_202602241100_EX</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2266,7 +2262,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241700_LV</t>
+          <t>SSEMG_STA_IS_202602241100_LV</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2283,7 +2279,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250700_AQ</t>
+          <t>SSEMG_COA_IS_202602250100_AQ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2300,7 +2296,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250700_NU</t>
+          <t>SSEMG_COA_IS_202602250100_NU</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2317,7 +2313,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250700_EX</t>
+          <t>SSEMG_COA_IS_202602250100_EX</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2334,7 +2330,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250700_LV</t>
+          <t>SSEMG_COA_IS_202602250100_LV</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2351,7 +2347,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231500_AQ</t>
+          <t>SSEMG_STA_IS_202602231700_AQ</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2368,7 +2364,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231500_NU</t>
+          <t>SSEMG_STA_IS_202602231700_NU</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2385,7 +2381,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231500_EX</t>
+          <t>SSEMG_STA_IS_202602231700_EX</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2402,7 +2398,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231500_LV</t>
+          <t>SSEMG_STA_IS_202602231700_LV</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2419,7 +2415,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602242300_AQ</t>
+          <t>SSEMG_STA_IS_202602241700_AQ</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2436,7 +2432,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602242300_NU</t>
+          <t>SSEMG_STA_IS_202602241700_NU</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2453,7 +2449,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602242300_EX</t>
+          <t>SSEMG_STA_IS_202602241700_EX</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2470,7 +2466,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602242300_LV</t>
+          <t>SSEMG_STA_IS_202602241700_LV</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2487,7 +2483,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241500_AQ</t>
+          <t>SSEMG_COA_IS_202602241500_AQ</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2504,7 +2500,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241500_NU</t>
+          <t>SSEMG_COA_IS_202602241500_NU</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2521,7 +2517,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241500_EX</t>
+          <t>SSEMG_COA_IS_202602241500_EX</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2538,7 +2534,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241500_LV</t>
+          <t>SSEMG_COA_IS_202602241500_LV</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2555,7 +2551,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241900_AQ</t>
+          <t>SSEMG_COA_IS_202602241300_AQ</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2572,7 +2568,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241900_NU</t>
+          <t>SSEMG_COA_IS_202602241300_NU</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2589,7 +2585,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241900_EX</t>
+          <t>SSEMG_COA_IS_202602241300_EX</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2606,7 +2602,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241900_LV</t>
+          <t>SSEMG_COA_IS_202602241300_LV</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2623,7 +2619,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602251300_AQ</t>
+          <t>SSEMG_STA_IS_202602241500_AQ</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2640,7 +2636,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602251300_NU</t>
+          <t>SSEMG_STA_IS_202602241500_NU</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2657,7 +2653,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602251300_EX</t>
+          <t>SSEMG_STA_IS_202602241500_EX</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2674,7 +2670,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602251300_LV</t>
+          <t>SSEMG_STA_IS_202602241500_LV</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2691,7 +2687,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240100_AQ</t>
+          <t>SSEMG_STA_IS_202602241900_AQ</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2708,7 +2704,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240100_NU</t>
+          <t>SSEMG_STA_IS_202602241900_NU</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2725,7 +2721,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240100_EX</t>
+          <t>SSEMG_STA_IS_202602241900_EX</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2742,7 +2738,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240100_LV</t>
+          <t>SSEMG_STA_IS_202602241900_LV</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2759,7 +2755,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602232300_AQ</t>
+          <t>SSEMG_COA_IS_202602240100_AQ</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2776,7 +2772,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602232300_NU</t>
+          <t>SSEMG_COA_IS_202602240100_NU</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2793,7 +2789,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602232300_EX</t>
+          <t>SSEMG_COA_IS_202602240100_EX</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2810,7 +2806,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602232300_LV</t>
+          <t>SSEMG_COA_IS_202602240100_LV</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2827,7 +2823,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250100_AQ</t>
+          <t>SSEMG_STA_IS_202602240700_AQ</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2844,7 +2840,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250100_NU</t>
+          <t>SSEMG_STA_IS_202602240700_NU</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2861,7 +2857,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250100_EX</t>
+          <t>SSEMG_STA_IS_202602240700_EX</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2878,7 +2874,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250100_LV</t>
+          <t>SSEMG_STA_IS_202602240700_LV</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2895,7 +2891,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602231900_AQ</t>
+          <t>SSEMG_STA_IS_202602231500_AQ</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2912,7 +2908,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602231900_NU</t>
+          <t>SSEMG_STA_IS_202602231500_NU</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2929,7 +2925,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602231900_EX</t>
+          <t>SSEMG_STA_IS_202602231500_EX</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2946,7 +2942,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602231900_LV</t>
+          <t>SSEMG_STA_IS_202602231500_LV</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2963,7 +2959,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241100_AQ</t>
+          <t>SSEMG_COA_IS_202602232300_AQ</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2980,7 +2976,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241100_NU</t>
+          <t>SSEMG_COA_IS_202602232300_NU</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2997,7 +2993,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241100_EX</t>
+          <t>SSEMG_COA_IS_202602232300_EX</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3014,7 +3010,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241100_LV</t>
+          <t>SSEMG_COA_IS_202602232300_LV</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3031,7 +3027,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602232300_AQ</t>
+          <t>SSEMG_COA_IS_202602240700_AQ</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3048,7 +3044,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602232300_NU</t>
+          <t>SSEMG_COA_IS_202602240700_NU</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3065,7 +3061,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602232300_EX</t>
+          <t>SSEMG_COA_IS_202602240700_EX</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3082,7 +3078,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602232300_LV</t>
+          <t>SSEMG_COA_IS_202602240700_LV</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3099,7 +3095,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231900_AQ</t>
+          <t>SSEMG_STA_IS_202602251300_AQ</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3116,7 +3112,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231900_NU</t>
+          <t>SSEMG_STA_IS_202602251300_NU</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3133,7 +3129,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231900_EX</t>
+          <t>SSEMG_STA_IS_202602251300_EX</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3150,7 +3146,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231900_LV</t>
+          <t>SSEMG_STA_IS_202602251300_LV</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3167,7 +3163,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240300_AQ</t>
+          <t>SSEMG_STA_IS_202602250300_AQ</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3184,7 +3180,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240300_NU</t>
+          <t>SSEMG_STA_IS_202602250300_NU</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3201,7 +3197,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240300_EX</t>
+          <t>SSEMG_STA_IS_202602250300_EX</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3218,7 +3214,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240300_LV</t>
+          <t>SSEMG_STA_IS_202602250300_LV</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3235,7 +3231,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240900_AQ</t>
+          <t>SSEMG_COA_IS_202602231900_AQ</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3252,7 +3248,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240900_NU</t>
+          <t>SSEMG_COA_IS_202602231900_NU</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3269,7 +3265,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240900_EX</t>
+          <t>SSEMG_COA_IS_202602231900_EX</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3286,7 +3282,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240900_LV</t>
+          <t>SSEMG_COA_IS_202602231900_LV</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3303,7 +3299,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241300_AQ</t>
+          <t>SSEMG_COA_IS_202602250500_AQ</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3320,7 +3316,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241300_NU</t>
+          <t>SSEMG_COA_IS_202602250500_NU</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3337,7 +3333,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241300_EX</t>
+          <t>SSEMG_COA_IS_202602250500_EX</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3354,7 +3350,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241300_LV</t>
+          <t>SSEMG_COA_IS_202602250500_LV</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3371,7 +3367,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250900_AQ</t>
+          <t>SSEMG_COA_IS_202602240300_AQ</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3388,7 +3384,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250900_NU</t>
+          <t>SSEMG_COA_IS_202602240300_NU</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3405,7 +3401,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250900_EX</t>
+          <t>SSEMG_COA_IS_202602240300_EX</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3422,7 +3418,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250900_LV</t>
+          <t>SSEMG_COA_IS_202602240300_LV</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3439,7 +3435,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250900_AQ</t>
+          <t>SSEMG_STA_IS_202602240100_AQ</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3456,7 +3452,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250900_NU</t>
+          <t>SSEMG_STA_IS_202602240100_NU</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3473,7 +3469,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250900_EX</t>
+          <t>SSEMG_STA_IS_202602240100_EX</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3490,7 +3486,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250900_LV</t>
+          <t>SSEMG_STA_IS_202602240100_LV</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3507,7 +3503,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241300_AQ</t>
+          <t>SSEMG_COA_IS_202602241700_AQ</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3524,7 +3520,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241300_NU</t>
+          <t>SSEMG_COA_IS_202602241700_NU</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3541,7 +3537,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241300_EX</t>
+          <t>SSEMG_COA_IS_202602241700_EX</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3558,7 +3554,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241300_LV</t>
+          <t>SSEMG_COA_IS_202602241700_LV</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3575,7 +3571,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602231700_AQ</t>
+          <t>SSEMG_COA_IS_202602250300_AQ</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3592,7 +3588,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602231700_NU</t>
+          <t>SSEMG_COA_IS_202602250300_NU</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3609,7 +3605,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602231700_EX</t>
+          <t>SSEMG_COA_IS_202602250300_EX</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3626,7 +3622,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602231700_LV</t>
+          <t>SSEMG_COA_IS_202602250300_LV</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3643,7 +3639,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602242100_AQ</t>
+          <t>SSEMG_COA_IS_202602240500_AQ</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3660,7 +3656,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602242100_NU</t>
+          <t>SSEMG_COA_IS_202602240500_NU</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3677,7 +3673,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602242100_EX</t>
+          <t>SSEMG_COA_IS_202602240500_EX</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3694,7 +3690,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602242100_LV</t>
+          <t>SSEMG_COA_IS_202602240500_LV</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3711,7 +3707,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602242300_AQ</t>
+          <t>SSEMG_COA_IS_202602251300_AQ</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3728,7 +3724,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602242300_NU</t>
+          <t>SSEMG_COA_IS_202602251300_NU</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3745,7 +3741,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602242300_EX</t>
+          <t>SSEMG_COA_IS_202602251300_EX</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3762,7 +3758,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602242300_LV</t>
+          <t>SSEMG_COA_IS_202602251300_LV</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -3779,7 +3775,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240700_AQ</t>
+          <t>SSEMG_STA_IS_202602241300_AQ</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3796,7 +3792,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240700_NU</t>
+          <t>SSEMG_STA_IS_202602241300_NU</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3813,7 +3809,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240700_EX</t>
+          <t>SSEMG_STA_IS_202602241300_EX</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3830,7 +3826,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240700_LV</t>
+          <t>SSEMG_STA_IS_202602241300_LV</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3847,7 +3843,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241100_AQ</t>
+          <t>SSEMG_STA_IS_202602242300_AQ</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3864,7 +3860,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241100_NU</t>
+          <t>SSEMG_STA_IS_202602242300_NU</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3881,7 +3877,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241100_EX</t>
+          <t>SSEMG_STA_IS_202602242300_EX</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -3898,7 +3894,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241100_LV</t>
+          <t>SSEMG_STA_IS_202602242300_LV</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3915,7 +3911,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250300_AQ</t>
+          <t>SSEMG_STA_IS_202602240300_AQ</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3932,7 +3928,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250300_NU</t>
+          <t>SSEMG_STA_IS_202602240300_NU</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3949,7 +3945,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250300_EX</t>
+          <t>SSEMG_STA_IS_202602240300_EX</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3966,7 +3962,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250300_LV</t>
+          <t>SSEMG_STA_IS_202602240300_LV</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -3983,7 +3979,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240500_AQ</t>
+          <t>SSEMG_STA_IS_202602250900_AQ</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4000,7 +3996,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240500_NU</t>
+          <t>SSEMG_STA_IS_202602250900_NU</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4017,7 +4013,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240500_EX</t>
+          <t>SSEMG_STA_IS_202602250900_EX</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4034,7 +4030,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240500_LV</t>
+          <t>SSEMG_STA_IS_202602250900_LV</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4051,7 +4047,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602251100_AQ</t>
+          <t>SSEMG_COA_IS_202602241100_AQ</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4068,7 +4064,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602251100_NU</t>
+          <t>SSEMG_COA_IS_202602241100_NU</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4085,7 +4081,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602251100_EX</t>
+          <t>SSEMG_COA_IS_202602241100_EX</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4102,7 +4098,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602251100_LV</t>
+          <t>SSEMG_COA_IS_202602241100_LV</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4119,7 +4115,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250500_AQ</t>
+          <t>SSEMG_STA_IS_202602250100_AQ</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4136,7 +4132,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250500_NU</t>
+          <t>SSEMG_STA_IS_202602250100_NU</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4153,7 +4149,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250500_EX</t>
+          <t>SSEMG_STA_IS_202602250100_EX</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4170,7 +4166,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250500_LV</t>
+          <t>SSEMG_STA_IS_202602250100_LV</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4187,7 +4183,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241700_AQ</t>
+          <t>SSEMG_STA_IS_202602240500_AQ</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4204,7 +4200,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241700_NU</t>
+          <t>SSEMG_STA_IS_202602240500_NU</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4221,7 +4217,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241700_EX</t>
+          <t>SSEMG_STA_IS_202602240500_EX</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4238,7 +4234,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241700_LV</t>
+          <t>SSEMG_STA_IS_202602240500_LV</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4255,7 +4251,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602251300_AQ</t>
+          <t>SSEMG_STA_IS_202602231900_AQ</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4272,7 +4268,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602251300_NU</t>
+          <t>SSEMG_STA_IS_202602231900_NU</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4289,7 +4285,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602251300_EX</t>
+          <t>SSEMG_STA_IS_202602231900_EX</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4306,7 +4302,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602251300_LV</t>
+          <t>SSEMG_STA_IS_202602231900_LV</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4323,7 +4319,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250300_AQ</t>
+          <t>SSEMG_STA_IS_202602250700_AQ</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4340,7 +4336,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250300_NU</t>
+          <t>SSEMG_STA_IS_202602250700_NU</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4357,7 +4353,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250300_EX</t>
+          <t>SSEMG_STA_IS_202602250700_EX</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4374,7 +4370,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250300_LV</t>
+          <t>SSEMG_STA_IS_202602250700_LV</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4397,9 +4393,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="20.7109375" style="2" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
@@ -4409,7 +4402,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>time_PST</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -4439,8 +4432,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B2" s="2">
-        <v>46076.95833333333</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-02-23 15:00:00</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4453,7 +4448,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -4465,8 +4460,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B3" s="2">
-        <v>46077.04166666667</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-02-23 17:00:00</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -4479,7 +4476,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -4491,8 +4488,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B4" s="2">
-        <v>46077.125</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-02-23 19:00:00</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4505,7 +4504,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -4517,8 +4516,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B5" s="2">
-        <v>46077.20833333333</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-02-23 21:00:00</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -4531,7 +4532,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -4543,8 +4544,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B6" s="2">
-        <v>46077.29166666667</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-02-23 23:00:00</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -4557,7 +4560,7 @@
         </is>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4569,8 +4572,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B7" s="2">
-        <v>46077.375</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-02-24 01:00:00</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -4583,7 +4588,7 @@
         </is>
       </c>
       <c r="E7">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -4595,8 +4600,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B8" s="2">
-        <v>46077.45833333333</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-02-24 03:00:00</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -4609,7 +4616,7 @@
         </is>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -4621,8 +4628,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B9" s="2">
-        <v>46077.54166666667</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-02-24 05:00:00</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -4635,7 +4644,7 @@
         </is>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -4647,8 +4656,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B10" s="2">
-        <v>46077.625</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-02-24 07:00:00</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -4661,7 +4672,7 @@
         </is>
       </c>
       <c r="E10">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F10">
         <v>9</v>
@@ -4673,8 +4684,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B11" s="2">
-        <v>46077.70833333333</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-02-24 09:00:00</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -4687,7 +4700,7 @@
         </is>
       </c>
       <c r="E11">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -4699,8 +4712,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B12" s="2">
-        <v>46077.79166666667</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:00:00</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -4713,7 +4728,7 @@
         </is>
       </c>
       <c r="E12">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F12">
         <v>11</v>
@@ -4725,8 +4740,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B13" s="2">
-        <v>46077.875</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-02-24 13:00:00</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -4739,7 +4756,7 @@
         </is>
       </c>
       <c r="E13">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -4751,8 +4768,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <v>46077.95833333333</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-02-24 15:00:00</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -4765,7 +4784,7 @@
         </is>
       </c>
       <c r="E14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F14">
         <v>13</v>
@@ -4777,8 +4796,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B15" s="2">
-        <v>46078.04166666667</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-02-24 17:00:00</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -4791,7 +4812,7 @@
         </is>
       </c>
       <c r="E15">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="F15">
         <v>14</v>
@@ -4803,8 +4824,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B16" s="2">
-        <v>46078.125</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-02-24 19:00:00</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -4817,7 +4840,7 @@
         </is>
       </c>
       <c r="E16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F16">
         <v>15</v>
@@ -4829,8 +4852,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B17" s="2">
-        <v>46078.20833333333</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-02-24 21:00:00</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -4843,7 +4868,7 @@
         </is>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F17">
         <v>16</v>
@@ -4855,8 +4880,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <v>46078.29166666667</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-02-24 23:00:00</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -4869,7 +4896,7 @@
         </is>
       </c>
       <c r="E18">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="F18">
         <v>17</v>
@@ -4881,8 +4908,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B19" s="2">
-        <v>46078.375</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-02-25 01:00:00</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -4895,7 +4924,7 @@
         </is>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="F19">
         <v>18</v>
@@ -4907,8 +4936,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B20" s="2">
-        <v>46078.45833333333</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-02-25 03:00:00</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -4921,7 +4952,7 @@
         </is>
       </c>
       <c r="E20">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F20">
         <v>19</v>
@@ -4933,8 +4964,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B21" s="2">
-        <v>46078.54166666667</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-02-25 05:00:00</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -4947,7 +4980,7 @@
         </is>
       </c>
       <c r="E21">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F21">
         <v>20</v>
@@ -4959,8 +4992,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B22" s="2">
-        <v>46078.625</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-02-25 07:00:00</t>
+        </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -4973,7 +5008,7 @@
         </is>
       </c>
       <c r="E22">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="F22">
         <v>21</v>
@@ -4985,8 +5020,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B23" s="2">
-        <v>46078.70833333333</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:00:00</t>
+        </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -4999,7 +5036,7 @@
         </is>
       </c>
       <c r="E23">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F23">
         <v>22</v>
@@ -5011,8 +5048,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B24" s="2">
-        <v>46078.79166666667</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:00:00</t>
+        </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -5025,7 +5064,7 @@
         </is>
       </c>
       <c r="E24">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="F24">
         <v>23</v>
@@ -5037,8 +5076,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B25" s="2">
-        <v>46078.875</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:00:00</t>
+        </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -5051,7 +5092,7 @@
         </is>
       </c>
       <c r="E25">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F25">
         <v>24</v>
@@ -5063,8 +5104,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B26" s="2">
-        <v>46077.04166666667</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-02-23 17:00:00</t>
+        </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -5077,7 +5120,7 @@
         </is>
       </c>
       <c r="E26">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -5089,8 +5132,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B27" s="2">
-        <v>46077.125</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-02-23 19:00:00</t>
+        </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -5103,7 +5148,7 @@
         </is>
       </c>
       <c r="E27">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F27">
         <v>2</v>
@@ -5115,8 +5160,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B28" s="2">
-        <v>46077.20833333333</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-02-23 21:00:00</t>
+        </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -5129,7 +5176,7 @@
         </is>
       </c>
       <c r="E28">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F28">
         <v>3</v>
@@ -5141,8 +5188,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B29" s="2">
-        <v>46077.29166666667</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-02-23 23:00:00</t>
+        </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -5155,7 +5204,7 @@
         </is>
       </c>
       <c r="E29">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F29">
         <v>4</v>
@@ -5167,8 +5216,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B30" s="2">
-        <v>46077.375</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-02-24 01:00:00</t>
+        </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -5181,7 +5232,7 @@
         </is>
       </c>
       <c r="E30">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F30">
         <v>5</v>
@@ -5193,8 +5244,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B31" s="2">
-        <v>46077.45833333333</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-02-24 03:00:00</t>
+        </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -5207,7 +5260,7 @@
         </is>
       </c>
       <c r="E31">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F31">
         <v>6</v>
@@ -5219,8 +5272,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B32" s="2">
-        <v>46077.54166666667</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-02-24 05:00:00</t>
+        </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5233,7 +5288,7 @@
         </is>
       </c>
       <c r="E32">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F32">
         <v>7</v>
@@ -5245,8 +5300,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B33" s="2">
-        <v>46077.625</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-02-24 07:00:00</t>
+        </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5259,7 +5316,7 @@
         </is>
       </c>
       <c r="E33">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F33">
         <v>8</v>
@@ -5271,8 +5328,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B34" s="2">
-        <v>46077.70833333333</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-02-24 09:00:00</t>
+        </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5285,7 +5344,7 @@
         </is>
       </c>
       <c r="E34">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F34">
         <v>9</v>
@@ -5297,8 +5356,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B35" s="2">
-        <v>46077.79166666667</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:00:00</t>
+        </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5311,7 +5372,7 @@
         </is>
       </c>
       <c r="E35">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F35">
         <v>10</v>
@@ -5323,8 +5384,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B36" s="2">
-        <v>46077.875</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-02-24 13:00:00</t>
+        </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5337,7 +5400,7 @@
         </is>
       </c>
       <c r="E36">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F36">
         <v>11</v>
@@ -5349,8 +5412,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B37" s="2">
-        <v>46077.95833333333</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-02-24 15:00:00</t>
+        </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5363,7 +5428,7 @@
         </is>
       </c>
       <c r="E37">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F37">
         <v>12</v>
@@ -5375,8 +5440,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B38" s="2">
-        <v>46078.04166666667</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-02-24 17:00:00</t>
+        </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5389,7 +5456,7 @@
         </is>
       </c>
       <c r="E38">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F38">
         <v>13</v>
@@ -5401,8 +5468,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B39" s="2">
-        <v>46078.125</v>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-02-24 19:00:00</t>
+        </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5415,7 +5484,7 @@
         </is>
       </c>
       <c r="E39">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F39">
         <v>14</v>
@@ -5427,8 +5496,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B40" s="2">
-        <v>46078.20833333333</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-02-24 21:00:00</t>
+        </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5441,7 +5512,7 @@
         </is>
       </c>
       <c r="E40">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="F40">
         <v>15</v>
@@ -5453,8 +5524,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B41" s="2">
-        <v>46078.29166666667</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-02-24 23:00:00</t>
+        </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5467,7 +5540,7 @@
         </is>
       </c>
       <c r="E41">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="F41">
         <v>16</v>
@@ -5479,8 +5552,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B42" s="2">
-        <v>46078.375</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-02-25 01:00:00</t>
+        </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5493,7 +5568,7 @@
         </is>
       </c>
       <c r="E42">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F42">
         <v>17</v>
@@ -5505,8 +5580,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B43" s="2">
-        <v>46078.45833333333</v>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-02-25 03:00:00</t>
+        </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5519,7 +5596,7 @@
         </is>
       </c>
       <c r="E43">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F43">
         <v>18</v>
@@ -5531,8 +5608,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B44" s="2">
-        <v>46078.54166666667</v>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-02-25 05:00:00</t>
+        </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5545,7 +5624,7 @@
         </is>
       </c>
       <c r="E44">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F44">
         <v>19</v>
@@ -5557,8 +5636,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B45" s="2">
-        <v>46078.625</v>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-02-25 07:00:00</t>
+        </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5571,7 +5652,7 @@
         </is>
       </c>
       <c r="E45">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F45">
         <v>20</v>
@@ -5583,8 +5664,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B46" s="2">
-        <v>46078.70833333333</v>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:00:00</t>
+        </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5597,7 +5680,7 @@
         </is>
       </c>
       <c r="E46">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F46">
         <v>21</v>
@@ -5609,8 +5692,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B47" s="2">
-        <v>46078.79166666667</v>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:00:00</t>
+        </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5623,7 +5708,7 @@
         </is>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F47">
         <v>22</v>
@@ -5635,8 +5720,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B48" s="2">
-        <v>46078.875</v>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:00:00</t>
+        </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5649,7 +5736,7 @@
         </is>
       </c>
       <c r="E48">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F48">
         <v>23</v>
@@ -5661,8 +5748,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B49" s="2">
-        <v>46078.95833333333</v>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-02-25 15:00:00</t>
+        </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/Templates/water-quality-analysis/Test_code/SSEMG_IS_20260224_label-table.xlsx
+++ b/Templates/water-quality-analysis/Test_code/SSEMG_IS_20260224_label-table.xlsx
@@ -18,9 +18,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd HH:mm:ss UTC"/>
-  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -58,12 +55,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -364,12 +360,12 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>sample_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>field_sample_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>sample_name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -381,12 +377,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>SSEMG_R0002</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602231500</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SSEMG_R0012</t>
         </is>
       </c>
       <c r="C2">
@@ -396,12 +392,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>SSEMG_R0005</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602231700</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>SSEMG_R0011</t>
         </is>
       </c>
       <c r="C3">
@@ -411,12 +407,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>SSEMG_R0033</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602231900</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SSEMG_R0043</t>
         </is>
       </c>
       <c r="C4">
@@ -426,12 +422,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>SSEMG_R0015</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602232100</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SSEMG_R0017</t>
         </is>
       </c>
       <c r="C5">
@@ -441,12 +437,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>SSEMG_R0047</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602232300</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>SSEMG_R0010</t>
         </is>
       </c>
       <c r="C6">
@@ -456,12 +452,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>SSEMG_R0035</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602240100</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>SSEMG_R0030</t>
         </is>
       </c>
       <c r="C7">
@@ -471,12 +467,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>SSEMG_R0037</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602240300</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>SSEMG_R0039</t>
         </is>
       </c>
       <c r="C8">
@@ -486,12 +482,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>SSEMG_R0019</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602240500</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>SSEMG_R0014</t>
         </is>
       </c>
       <c r="C9">
@@ -501,12 +497,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>SSEMG_R0004</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602240700</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>SSEMG_R0022</t>
         </is>
       </c>
       <c r="C10">
@@ -516,12 +512,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>SSEMG_R0021</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602240900</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SSEMG_R0008</t>
         </is>
       </c>
       <c r="C11">
@@ -531,12 +527,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>SSEMG_R0026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602241100</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SSEMG_R0020</t>
         </is>
       </c>
       <c r="C12">
@@ -546,12 +542,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>SSEMG_R0045</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602241300</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SSEMG_R0036</t>
         </is>
       </c>
       <c r="C13">
@@ -561,12 +557,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>SSEMG_R0020</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602241500</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SSEMG_R0034</t>
         </is>
       </c>
       <c r="C14">
@@ -576,12 +572,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>SSEMG_R0013</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602241700</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>SSEMG_R0005</t>
         </is>
       </c>
       <c r="C15">
@@ -591,12 +587,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>SSEMG_R0042</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602241900</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>SSEMG_R0026</t>
         </is>
       </c>
       <c r="C16">
@@ -606,12 +602,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>SSEMG_R0011</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602242100</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>SSEMG_R0025</t>
         </is>
       </c>
       <c r="C17">
@@ -621,12 +617,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>SSEMG_R0006</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602242300</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>SSEMG_R0033</t>
         </is>
       </c>
       <c r="C18">
@@ -636,12 +632,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>SSEMG_R0003</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602250100</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>SSEMG_R0037</t>
         </is>
       </c>
       <c r="C19">
@@ -651,12 +647,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>SSEMG_R0046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602250300</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>SSEMG_R0048</t>
         </is>
       </c>
       <c r="C20">
@@ -666,12 +662,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>SSEMG_R0016</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602250500</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>SSEMG_R0027</t>
         </is>
       </c>
       <c r="C21">
@@ -681,12 +677,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>SSEMG_R0014</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602250700</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>SSEMG_R0004</t>
         </is>
       </c>
       <c r="C22">
@@ -696,12 +692,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>SSEMG_R0025</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602250900</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>SSEMG_R0016</t>
         </is>
       </c>
       <c r="C23">
@@ -711,12 +707,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>SSEMG_R0039</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602251100</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>SSEMG_R0028</t>
         </is>
       </c>
       <c r="C24">
@@ -726,12 +722,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>SSEMG_R0018</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>SSEMG_STA_IS_202602251300</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>SSEMG_R0045</t>
         </is>
       </c>
       <c r="C25">
@@ -741,12 +737,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>SSEMG_R0043</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602231700</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>SSEMG_R0006</t>
         </is>
       </c>
       <c r="C26">
@@ -756,12 +752,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>SSEMG_R0036</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602231900</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>SSEMG_R0038</t>
         </is>
       </c>
       <c r="C27">
@@ -771,12 +767,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>SSEMG_R0024</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602232100</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>SSEMG_R0040</t>
         </is>
       </c>
       <c r="C28">
@@ -786,12 +782,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>SSEMG_R0001</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602232300</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>SSEMG_R0041</t>
         </is>
       </c>
       <c r="C29">
@@ -801,12 +797,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>SSEMG_R0034</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602240100</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>SSEMG_R0035</t>
         </is>
       </c>
       <c r="C30">
@@ -816,12 +812,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>SSEMG_R0032</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602240300</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>SSEMG_R0015</t>
         </is>
       </c>
       <c r="C31">
@@ -831,12 +827,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>SSEMG_R0028</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602240500</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>SSEMG_R0044</t>
         </is>
       </c>
       <c r="C32">
@@ -846,12 +842,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>SSEMG_R0010</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602240700</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>SSEMG_R0002</t>
         </is>
       </c>
       <c r="C33">
@@ -861,12 +857,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>SSEMG_R0041</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602240900</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>SSEMG_R0023</t>
         </is>
       </c>
       <c r="C34">
@@ -876,12 +872,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>SSEMG_R0007</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602241100</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>SSEMG_R0029</t>
         </is>
       </c>
       <c r="C35">
@@ -891,12 +887,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>SSEMG_R0012</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602241300</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>SSEMG_R0003</t>
         </is>
       </c>
       <c r="C36">
@@ -906,12 +902,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>SSEMG_R0030</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602241500</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>SSEMG_R0047</t>
         </is>
       </c>
       <c r="C37">
@@ -921,12 +917,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>SSEMG_R0023</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602241700</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>SSEMG_R0021</t>
         </is>
       </c>
       <c r="C38">
@@ -936,12 +932,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>SSEMG_R0027</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602241900</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>SSEMG_R0019</t>
         </is>
       </c>
       <c r="C39">
@@ -951,12 +947,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>SSEMG_R0040</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602242100</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>SSEMG_R0031</t>
         </is>
       </c>
       <c r="C40">
@@ -966,12 +962,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>SSEMG_R0009</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602242300</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>SSEMG_R0013</t>
         </is>
       </c>
       <c r="C41">
@@ -981,12 +977,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>SSEMG_R0029</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602250100</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>SSEMG_R0046</t>
         </is>
       </c>
       <c r="C42">
@@ -996,12 +992,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>SSEMG_R0044</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602250300</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>SSEMG_R0042</t>
         </is>
       </c>
       <c r="C43">
@@ -1011,12 +1007,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>SSEMG_R0008</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602250500</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>SSEMG_R0024</t>
         </is>
       </c>
       <c r="C44">
@@ -1026,12 +1022,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>SSEMG_R0038</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602250700</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>SSEMG_R0009</t>
         </is>
       </c>
       <c r="C45">
@@ -1041,12 +1037,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>SSEMG_R0022</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602250900</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>SSEMG_R0018</t>
         </is>
       </c>
       <c r="C46">
@@ -1056,12 +1052,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>SSEMG_R0017</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602251100</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>SSEMG_R0001</t>
         </is>
       </c>
       <c r="C47">
@@ -1071,12 +1067,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>SSEMG_R0031</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602251300</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>SSEMG_R0032</t>
         </is>
       </c>
       <c r="C48">
@@ -1086,12 +1082,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>SSEMG_R0048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>SSEMG_COA_IS_202602251500</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>SSEMG_R0007</t>
         </is>
       </c>
       <c r="C49">
@@ -1105,744 +1101,595 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>sample_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>field_sample_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>sample_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>botnum</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602232100</t>
+          <t>SSEMG_R0001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SSEMG_R0001</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>4</v>
+          <t>SSEMG_COA_IS_202602232300</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240300</t>
+          <t>SSEMG_R0002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SSEMG_R0002</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>6</v>
+          <t>SSEMG_STA_IS_202602231500</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241700</t>
+          <t>SSEMG_R0003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SSEMG_R0003</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>13</v>
+          <t>SSEMG_STA_IS_202602250100</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241900</t>
+          <t>SSEMG_R0004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SSEMG_R0004</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>14</v>
+          <t>SSEMG_STA_IS_202602240700</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602242300</t>
+          <t>SSEMG_R0005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SSEMG_R0005</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>16</v>
+          <t>SSEMG_STA_IS_202602231700</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241300</t>
+          <t>SSEMG_R0006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SSEMG_R0006</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>11</v>
+          <t>SSEMG_STA_IS_202602242300</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250100</t>
+          <t>SSEMG_R0007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SSEMG_R0007</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>17</v>
+          <t>SSEMG_COA_IS_202602241100</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240300</t>
+          <t>SSEMG_R0008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SSEMG_R0008</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>7</v>
+          <t>SSEMG_COA_IS_202602250500</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602251100</t>
+          <t>SSEMG_R0009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SSEMG_R0009</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>23</v>
+          <t>SSEMG_COA_IS_202602242300</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250500</t>
+          <t>SSEMG_R0010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SSEMG_R0010</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>19</v>
+          <t>SSEMG_COA_IS_202602240700</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241300</t>
+          <t>SSEMG_R0011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SSEMG_R0011</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>12</v>
+          <t>SSEMG_STA_IS_202602242100</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602232300</t>
+          <t>SSEMG_R0012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SSEMG_R0012</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>5</v>
+          <t>SSEMG_COA_IS_202602241300</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250700</t>
+          <t>SSEMG_R0013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SSEMG_R0013</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>21</v>
+          <t>SSEMG_STA_IS_202602241700</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240900</t>
+          <t>SSEMG_R0014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SSEMG_R0014</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>10</v>
+          <t>SSEMG_STA_IS_202602250700</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240700</t>
+          <t>SSEMG_R0015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SSEMG_R0015</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>8</v>
+          <t>SSEMG_STA_IS_202602232100</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231700</t>
+          <t>SSEMG_R0016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SSEMG_R0016</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>2</v>
+          <t>SSEMG_STA_IS_202602250500</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602231700</t>
+          <t>SSEMG_R0017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SSEMG_R0017</t>
-        </is>
-      </c>
-      <c r="C18">
-        <v>1</v>
+          <t>SSEMG_COA_IS_202602251100</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250300</t>
+          <t>SSEMG_R0018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SSEMG_R0018</t>
-        </is>
-      </c>
-      <c r="C19">
-        <v>18</v>
+          <t>SSEMG_STA_IS_202602251300</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240900</t>
+          <t>SSEMG_R0019</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SSEMG_R0019</t>
-        </is>
-      </c>
-      <c r="C20">
-        <v>9</v>
+          <t>SSEMG_STA_IS_202602240500</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241700</t>
+          <t>SSEMG_R0020</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SSEMG_R0020</t>
-        </is>
-      </c>
-      <c r="C21">
-        <v>14</v>
+          <t>SSEMG_STA_IS_202602241500</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250700</t>
+          <t>SSEMG_R0021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SSEMG_R0021</t>
-        </is>
-      </c>
-      <c r="C22">
-        <v>20</v>
+          <t>SSEMG_STA_IS_202602240900</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250900</t>
+          <t>SSEMG_R0022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SSEMG_R0022</t>
-        </is>
-      </c>
-      <c r="C23">
-        <v>22</v>
+          <t>SSEMG_COA_IS_202602250900</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240500</t>
+          <t>SSEMG_R0023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SSEMG_R0023</t>
-        </is>
-      </c>
-      <c r="C24">
-        <v>7</v>
+          <t>SSEMG_COA_IS_202602241700</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602251500</t>
+          <t>SSEMG_R0024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SSEMG_R0024</t>
-        </is>
-      </c>
-      <c r="C25">
-        <v>24</v>
+          <t>SSEMG_COA_IS_202602232100</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250500</t>
+          <t>SSEMG_R0025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SSEMG_R0025</t>
-        </is>
-      </c>
-      <c r="C26">
-        <v>20</v>
+          <t>SSEMG_STA_IS_202602250900</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241500</t>
+          <t>SSEMG_R0026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SSEMG_R0026</t>
-        </is>
-      </c>
-      <c r="C27">
-        <v>12</v>
+          <t>SSEMG_STA_IS_202602241100</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602232100</t>
+          <t>SSEMG_R0027</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SSEMG_R0027</t>
-        </is>
-      </c>
-      <c r="C28">
-        <v>3</v>
+          <t>SSEMG_COA_IS_202602241900</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602251300</t>
+          <t>SSEMG_R0028</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SSEMG_R0028</t>
-        </is>
-      </c>
-      <c r="C29">
-        <v>23</v>
+          <t>SSEMG_COA_IS_202602240500</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241900</t>
+          <t>SSEMG_R0029</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SSEMG_R0029</t>
-        </is>
-      </c>
-      <c r="C30">
-        <v>15</v>
+          <t>SSEMG_COA_IS_202602250100</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241100</t>
+          <t>SSEMG_R0030</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SSEMG_R0030</t>
-        </is>
-      </c>
-      <c r="C31">
-        <v>11</v>
+          <t>SSEMG_COA_IS_202602241500</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240700</t>
+          <t>SSEMG_R0031</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SSEMG_R0031</t>
-        </is>
-      </c>
-      <c r="C32">
-        <v>9</v>
+          <t>SSEMG_COA_IS_202602251300</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231500</t>
+          <t>SSEMG_R0032</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SSEMG_R0032</t>
-        </is>
-      </c>
-      <c r="C33">
-        <v>1</v>
+          <t>SSEMG_COA_IS_202602240300</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602232300</t>
+          <t>SSEMG_R0033</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SSEMG_R0033</t>
-        </is>
-      </c>
-      <c r="C34">
-        <v>4</v>
+          <t>SSEMG_STA_IS_202602231900</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602242100</t>
+          <t>SSEMG_R0034</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SSEMG_R0034</t>
-        </is>
-      </c>
-      <c r="C35">
-        <v>15</v>
+          <t>SSEMG_COA_IS_202602240100</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602251300</t>
+          <t>SSEMG_R0035</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SSEMG_R0035</t>
-        </is>
-      </c>
-      <c r="C36">
-        <v>24</v>
+          <t>SSEMG_STA_IS_202602240100</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602251100</t>
+          <t>SSEMG_R0036</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SSEMG_R0036</t>
-        </is>
-      </c>
-      <c r="C37">
-        <v>22</v>
+          <t>SSEMG_COA_IS_202602231900</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250300</t>
+          <t>SSEMG_R0037</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SSEMG_R0037</t>
-        </is>
-      </c>
-      <c r="C38">
-        <v>19</v>
+          <t>SSEMG_STA_IS_202602240300</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250900</t>
+          <t>SSEMG_R0038</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SSEMG_R0038</t>
-        </is>
-      </c>
-      <c r="C39">
-        <v>21</v>
+          <t>SSEMG_COA_IS_202602250700</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240100</t>
+          <t>SSEMG_R0039</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SSEMG_R0039</t>
-        </is>
-      </c>
-      <c r="C40">
-        <v>6</v>
+          <t>SSEMG_STA_IS_202602251100</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602242100</t>
+          <t>SSEMG_R0040</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SSEMG_R0040</t>
-        </is>
-      </c>
-      <c r="C41">
-        <v>16</v>
+          <t>SSEMG_COA_IS_202602242100</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240100</t>
+          <t>SSEMG_R0041</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SSEMG_R0041</t>
-        </is>
-      </c>
-      <c r="C42">
-        <v>5</v>
+          <t>SSEMG_COA_IS_202602240900</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602231900</t>
+          <t>SSEMG_R0042</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SSEMG_R0042</t>
-        </is>
-      </c>
-      <c r="C43">
-        <v>2</v>
+          <t>SSEMG_STA_IS_202602241900</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241100</t>
+          <t>SSEMG_R0043</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SSEMG_R0043</t>
-        </is>
-      </c>
-      <c r="C44">
-        <v>10</v>
+          <t>SSEMG_COA_IS_202602231700</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602242300</t>
+          <t>SSEMG_R0044</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SSEMG_R0044</t>
-        </is>
-      </c>
-      <c r="C45">
-        <v>17</v>
+          <t>SSEMG_COA_IS_202602250300</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240500</t>
+          <t>SSEMG_R0045</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SSEMG_R0045</t>
-        </is>
-      </c>
-      <c r="C46">
-        <v>8</v>
+          <t>SSEMG_STA_IS_202602241300</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250100</t>
+          <t>SSEMG_R0046</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SSEMG_R0046</t>
-        </is>
-      </c>
-      <c r="C47">
-        <v>18</v>
+          <t>SSEMG_STA_IS_202602250300</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231900</t>
+          <t>SSEMG_R0047</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SSEMG_R0047</t>
-        </is>
-      </c>
-      <c r="C48">
-        <v>3</v>
+          <t>SSEMG_STA_IS_202602232300</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241500</t>
+          <t>SSEMG_R0048</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SSEMG_R0048</t>
-        </is>
-      </c>
-      <c r="C49">
-        <v>13</v>
+          <t>SSEMG_COA_IS_202602251500</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1858,12 +1705,12 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>sample_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>lab_sample_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>sample_name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -1875,12 +1722,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602232100_AQ</t>
+          <t>SSEMG_R0001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SSEMG_R0001</t>
+          <t>SSEMG_COA_IS_202602232300_AQ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1892,12 +1739,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602232100_NU</t>
+          <t>SSEMG_R0001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SSEMG_R0001</t>
+          <t>SSEMG_COA_IS_202602232300_NU</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1909,12 +1756,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602232100_EX</t>
+          <t>SSEMG_R0001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SSEMG_R0001</t>
+          <t>SSEMG_COA_IS_202602232300_EX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1926,12 +1773,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602232100_LV</t>
+          <t>SSEMG_R0001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SSEMG_R0001</t>
+          <t>SSEMG_COA_IS_202602232300_LV</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1943,12 +1790,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240300_AQ</t>
+          <t>SSEMG_R0002</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SSEMG_R0002</t>
+          <t>SSEMG_STA_IS_202602231500_AQ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1960,12 +1807,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240300_NU</t>
+          <t>SSEMG_R0002</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SSEMG_R0002</t>
+          <t>SSEMG_STA_IS_202602231500_NU</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1977,12 +1824,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240300_EX</t>
+          <t>SSEMG_R0002</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SSEMG_R0002</t>
+          <t>SSEMG_STA_IS_202602231500_EX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1994,12 +1841,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240300_LV</t>
+          <t>SSEMG_R0002</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SSEMG_R0002</t>
+          <t>SSEMG_STA_IS_202602231500_LV</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2011,12 +1858,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241700_AQ</t>
+          <t>SSEMG_R0003</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SSEMG_R0003</t>
+          <t>SSEMG_STA_IS_202602250100_AQ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2028,12 +1875,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241700_NU</t>
+          <t>SSEMG_R0003</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SSEMG_R0003</t>
+          <t>SSEMG_STA_IS_202602250100_NU</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2045,12 +1892,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241700_EX</t>
+          <t>SSEMG_R0003</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SSEMG_R0003</t>
+          <t>SSEMG_STA_IS_202602250100_EX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2062,12 +1909,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241700_LV</t>
+          <t>SSEMG_R0003</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SSEMG_R0003</t>
+          <t>SSEMG_STA_IS_202602250100_LV</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2079,12 +1926,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241900_AQ</t>
+          <t>SSEMG_R0004</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SSEMG_R0004</t>
+          <t>SSEMG_STA_IS_202602240700_AQ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2096,12 +1943,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241900_NU</t>
+          <t>SSEMG_R0004</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SSEMG_R0004</t>
+          <t>SSEMG_STA_IS_202602240700_NU</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2113,12 +1960,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241900_EX</t>
+          <t>SSEMG_R0004</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SSEMG_R0004</t>
+          <t>SSEMG_STA_IS_202602240700_EX</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2130,12 +1977,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241900_LV</t>
+          <t>SSEMG_R0004</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SSEMG_R0004</t>
+          <t>SSEMG_STA_IS_202602240700_LV</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2147,12 +1994,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602242300_AQ</t>
+          <t>SSEMG_R0005</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SSEMG_R0005</t>
+          <t>SSEMG_STA_IS_202602231700_AQ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2164,12 +2011,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602242300_NU</t>
+          <t>SSEMG_R0005</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SSEMG_R0005</t>
+          <t>SSEMG_STA_IS_202602231700_NU</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2181,12 +2028,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602242300_EX</t>
+          <t>SSEMG_R0005</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SSEMG_R0005</t>
+          <t>SSEMG_STA_IS_202602231700_EX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2198,12 +2045,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602242300_LV</t>
+          <t>SSEMG_R0005</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SSEMG_R0005</t>
+          <t>SSEMG_STA_IS_202602231700_LV</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2215,12 +2062,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241300_AQ</t>
+          <t>SSEMG_R0006</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SSEMG_R0006</t>
+          <t>SSEMG_STA_IS_202602242300_AQ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2232,12 +2079,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241300_NU</t>
+          <t>SSEMG_R0006</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SSEMG_R0006</t>
+          <t>SSEMG_STA_IS_202602242300_NU</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2249,12 +2096,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241300_EX</t>
+          <t>SSEMG_R0006</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SSEMG_R0006</t>
+          <t>SSEMG_STA_IS_202602242300_EX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2266,12 +2113,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241300_LV</t>
+          <t>SSEMG_R0006</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SSEMG_R0006</t>
+          <t>SSEMG_STA_IS_202602242300_LV</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2283,12 +2130,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250100_AQ</t>
+          <t>SSEMG_R0007</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SSEMG_R0007</t>
+          <t>SSEMG_COA_IS_202602241100_AQ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2300,12 +2147,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250100_NU</t>
+          <t>SSEMG_R0007</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SSEMG_R0007</t>
+          <t>SSEMG_COA_IS_202602241100_NU</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2317,12 +2164,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250100_EX</t>
+          <t>SSEMG_R0007</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SSEMG_R0007</t>
+          <t>SSEMG_COA_IS_202602241100_EX</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2334,12 +2181,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250100_LV</t>
+          <t>SSEMG_R0007</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SSEMG_R0007</t>
+          <t>SSEMG_COA_IS_202602241100_LV</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2351,12 +2198,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240300_AQ</t>
+          <t>SSEMG_R0008</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SSEMG_R0008</t>
+          <t>SSEMG_COA_IS_202602250500_AQ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2368,12 +2215,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240300_NU</t>
+          <t>SSEMG_R0008</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SSEMG_R0008</t>
+          <t>SSEMG_COA_IS_202602250500_NU</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2385,12 +2232,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240300_EX</t>
+          <t>SSEMG_R0008</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SSEMG_R0008</t>
+          <t>SSEMG_COA_IS_202602250500_EX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2402,12 +2249,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240300_LV</t>
+          <t>SSEMG_R0008</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SSEMG_R0008</t>
+          <t>SSEMG_COA_IS_202602250500_LV</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2419,12 +2266,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602251100_AQ</t>
+          <t>SSEMG_R0009</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SSEMG_R0009</t>
+          <t>SSEMG_COA_IS_202602242300_AQ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2436,12 +2283,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602251100_NU</t>
+          <t>SSEMG_R0009</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SSEMG_R0009</t>
+          <t>SSEMG_COA_IS_202602242300_NU</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2453,12 +2300,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602251100_EX</t>
+          <t>SSEMG_R0009</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SSEMG_R0009</t>
+          <t>SSEMG_COA_IS_202602242300_EX</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2470,12 +2317,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602251100_LV</t>
+          <t>SSEMG_R0009</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SSEMG_R0009</t>
+          <t>SSEMG_COA_IS_202602242300_LV</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2487,12 +2334,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250500_AQ</t>
+          <t>SSEMG_R0010</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SSEMG_R0010</t>
+          <t>SSEMG_COA_IS_202602240700_AQ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2504,12 +2351,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250500_NU</t>
+          <t>SSEMG_R0010</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SSEMG_R0010</t>
+          <t>SSEMG_COA_IS_202602240700_NU</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2521,12 +2368,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250500_EX</t>
+          <t>SSEMG_R0010</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SSEMG_R0010</t>
+          <t>SSEMG_COA_IS_202602240700_EX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2538,12 +2385,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250500_LV</t>
+          <t>SSEMG_R0010</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SSEMG_R0010</t>
+          <t>SSEMG_COA_IS_202602240700_LV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2555,12 +2402,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241300_AQ</t>
+          <t>SSEMG_R0011</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SSEMG_R0011</t>
+          <t>SSEMG_STA_IS_202602242100_AQ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2572,12 +2419,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241300_NU</t>
+          <t>SSEMG_R0011</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SSEMG_R0011</t>
+          <t>SSEMG_STA_IS_202602242100_NU</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2589,12 +2436,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241300_EX</t>
+          <t>SSEMG_R0011</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SSEMG_R0011</t>
+          <t>SSEMG_STA_IS_202602242100_EX</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2606,12 +2453,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241300_LV</t>
+          <t>SSEMG_R0011</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SSEMG_R0011</t>
+          <t>SSEMG_STA_IS_202602242100_LV</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2623,12 +2470,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602232300_AQ</t>
+          <t>SSEMG_R0012</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SSEMG_R0012</t>
+          <t>SSEMG_COA_IS_202602241300_AQ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2640,12 +2487,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602232300_NU</t>
+          <t>SSEMG_R0012</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SSEMG_R0012</t>
+          <t>SSEMG_COA_IS_202602241300_NU</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2657,12 +2504,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602232300_EX</t>
+          <t>SSEMG_R0012</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SSEMG_R0012</t>
+          <t>SSEMG_COA_IS_202602241300_EX</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2674,12 +2521,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602232300_LV</t>
+          <t>SSEMG_R0012</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SSEMG_R0012</t>
+          <t>SSEMG_COA_IS_202602241300_LV</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2691,12 +2538,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250700_AQ</t>
+          <t>SSEMG_R0013</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SSEMG_R0013</t>
+          <t>SSEMG_STA_IS_202602241700_AQ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2708,12 +2555,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250700_NU</t>
+          <t>SSEMG_R0013</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SSEMG_R0013</t>
+          <t>SSEMG_STA_IS_202602241700_NU</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2725,12 +2572,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250700_EX</t>
+          <t>SSEMG_R0013</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SSEMG_R0013</t>
+          <t>SSEMG_STA_IS_202602241700_EX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2742,12 +2589,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250700_LV</t>
+          <t>SSEMG_R0013</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SSEMG_R0013</t>
+          <t>SSEMG_STA_IS_202602241700_LV</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2759,12 +2606,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240900_AQ</t>
+          <t>SSEMG_R0014</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SSEMG_R0014</t>
+          <t>SSEMG_STA_IS_202602250700_AQ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2776,12 +2623,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240900_NU</t>
+          <t>SSEMG_R0014</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SSEMG_R0014</t>
+          <t>SSEMG_STA_IS_202602250700_NU</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2793,12 +2640,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240900_EX</t>
+          <t>SSEMG_R0014</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SSEMG_R0014</t>
+          <t>SSEMG_STA_IS_202602250700_EX</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2810,12 +2657,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240900_LV</t>
+          <t>SSEMG_R0014</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SSEMG_R0014</t>
+          <t>SSEMG_STA_IS_202602250700_LV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2827,12 +2674,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240700_AQ</t>
+          <t>SSEMG_R0015</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SSEMG_R0015</t>
+          <t>SSEMG_STA_IS_202602232100_AQ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2844,12 +2691,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240700_NU</t>
+          <t>SSEMG_R0015</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SSEMG_R0015</t>
+          <t>SSEMG_STA_IS_202602232100_NU</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2861,12 +2708,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240700_EX</t>
+          <t>SSEMG_R0015</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SSEMG_R0015</t>
+          <t>SSEMG_STA_IS_202602232100_EX</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2878,12 +2725,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240700_LV</t>
+          <t>SSEMG_R0015</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SSEMG_R0015</t>
+          <t>SSEMG_STA_IS_202602232100_LV</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2895,12 +2742,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231700_AQ</t>
+          <t>SSEMG_R0016</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SSEMG_R0016</t>
+          <t>SSEMG_STA_IS_202602250500_AQ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2912,12 +2759,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231700_NU</t>
+          <t>SSEMG_R0016</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SSEMG_R0016</t>
+          <t>SSEMG_STA_IS_202602250500_NU</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2929,12 +2776,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231700_EX</t>
+          <t>SSEMG_R0016</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SSEMG_R0016</t>
+          <t>SSEMG_STA_IS_202602250500_EX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2946,12 +2793,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231700_LV</t>
+          <t>SSEMG_R0016</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SSEMG_R0016</t>
+          <t>SSEMG_STA_IS_202602250500_LV</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2963,12 +2810,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602231700_AQ</t>
+          <t>SSEMG_R0017</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SSEMG_R0017</t>
+          <t>SSEMG_COA_IS_202602251100_AQ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2980,12 +2827,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602231700_NU</t>
+          <t>SSEMG_R0017</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SSEMG_R0017</t>
+          <t>SSEMG_COA_IS_202602251100_NU</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2997,12 +2844,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602231700_EX</t>
+          <t>SSEMG_R0017</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SSEMG_R0017</t>
+          <t>SSEMG_COA_IS_202602251100_EX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3014,12 +2861,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602231700_LV</t>
+          <t>SSEMG_R0017</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SSEMG_R0017</t>
+          <t>SSEMG_COA_IS_202602251100_LV</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3031,12 +2878,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250300_AQ</t>
+          <t>SSEMG_R0018</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SSEMG_R0018</t>
+          <t>SSEMG_STA_IS_202602251300_AQ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3048,12 +2895,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250300_NU</t>
+          <t>SSEMG_R0018</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SSEMG_R0018</t>
+          <t>SSEMG_STA_IS_202602251300_NU</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3065,12 +2912,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250300_EX</t>
+          <t>SSEMG_R0018</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SSEMG_R0018</t>
+          <t>SSEMG_STA_IS_202602251300_EX</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3082,12 +2929,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250300_LV</t>
+          <t>SSEMG_R0018</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SSEMG_R0018</t>
+          <t>SSEMG_STA_IS_202602251300_LV</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3099,12 +2946,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240900_AQ</t>
+          <t>SSEMG_R0019</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SSEMG_R0019</t>
+          <t>SSEMG_STA_IS_202602240500_AQ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3116,12 +2963,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240900_NU</t>
+          <t>SSEMG_R0019</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SSEMG_R0019</t>
+          <t>SSEMG_STA_IS_202602240500_NU</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3133,12 +2980,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240900_EX</t>
+          <t>SSEMG_R0019</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SSEMG_R0019</t>
+          <t>SSEMG_STA_IS_202602240500_EX</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3150,12 +2997,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240900_LV</t>
+          <t>SSEMG_R0019</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SSEMG_R0019</t>
+          <t>SSEMG_STA_IS_202602240500_LV</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3167,12 +3014,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241700_AQ</t>
+          <t>SSEMG_R0020</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SSEMG_R0020</t>
+          <t>SSEMG_STA_IS_202602241500_AQ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3184,12 +3031,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241700_NU</t>
+          <t>SSEMG_R0020</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SSEMG_R0020</t>
+          <t>SSEMG_STA_IS_202602241500_NU</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3201,12 +3048,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241700_EX</t>
+          <t>SSEMG_R0020</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SSEMG_R0020</t>
+          <t>SSEMG_STA_IS_202602241500_EX</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3218,12 +3065,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241700_LV</t>
+          <t>SSEMG_R0020</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SSEMG_R0020</t>
+          <t>SSEMG_STA_IS_202602241500_LV</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3235,12 +3082,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250700_AQ</t>
+          <t>SSEMG_R0021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SSEMG_R0021</t>
+          <t>SSEMG_STA_IS_202602240900_AQ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3252,12 +3099,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250700_NU</t>
+          <t>SSEMG_R0021</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SSEMG_R0021</t>
+          <t>SSEMG_STA_IS_202602240900_NU</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3269,12 +3116,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250700_EX</t>
+          <t>SSEMG_R0021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SSEMG_R0021</t>
+          <t>SSEMG_STA_IS_202602240900_EX</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3286,12 +3133,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250700_LV</t>
+          <t>SSEMG_R0021</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SSEMG_R0021</t>
+          <t>SSEMG_STA_IS_202602240900_LV</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3303,12 +3150,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250900_AQ</t>
+          <t>SSEMG_R0022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SSEMG_R0022</t>
+          <t>SSEMG_COA_IS_202602250900_AQ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3320,12 +3167,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250900_NU</t>
+          <t>SSEMG_R0022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SSEMG_R0022</t>
+          <t>SSEMG_COA_IS_202602250900_NU</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3337,12 +3184,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250900_EX</t>
+          <t>SSEMG_R0022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SSEMG_R0022</t>
+          <t>SSEMG_COA_IS_202602250900_EX</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3354,12 +3201,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250900_LV</t>
+          <t>SSEMG_R0022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SSEMG_R0022</t>
+          <t>SSEMG_COA_IS_202602250900_LV</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3371,12 +3218,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240500_AQ</t>
+          <t>SSEMG_R0023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SSEMG_R0023</t>
+          <t>SSEMG_COA_IS_202602241700_AQ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3388,12 +3235,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240500_NU</t>
+          <t>SSEMG_R0023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SSEMG_R0023</t>
+          <t>SSEMG_COA_IS_202602241700_NU</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3405,12 +3252,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240500_EX</t>
+          <t>SSEMG_R0023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SSEMG_R0023</t>
+          <t>SSEMG_COA_IS_202602241700_EX</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3422,12 +3269,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240500_LV</t>
+          <t>SSEMG_R0023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SSEMG_R0023</t>
+          <t>SSEMG_COA_IS_202602241700_LV</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3439,12 +3286,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602251500_AQ</t>
+          <t>SSEMG_R0024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SSEMG_R0024</t>
+          <t>SSEMG_COA_IS_202602232100_AQ</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3456,12 +3303,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602251500_NU</t>
+          <t>SSEMG_R0024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SSEMG_R0024</t>
+          <t>SSEMG_COA_IS_202602232100_NU</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3473,12 +3320,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602251500_EX</t>
+          <t>SSEMG_R0024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SSEMG_R0024</t>
+          <t>SSEMG_COA_IS_202602232100_EX</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3490,12 +3337,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602251500_LV</t>
+          <t>SSEMG_R0024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SSEMG_R0024</t>
+          <t>SSEMG_COA_IS_202602232100_LV</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3507,12 +3354,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250500_AQ</t>
+          <t>SSEMG_R0025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SSEMG_R0025</t>
+          <t>SSEMG_STA_IS_202602250900_AQ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3524,12 +3371,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250500_NU</t>
+          <t>SSEMG_R0025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SSEMG_R0025</t>
+          <t>SSEMG_STA_IS_202602250900_NU</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3541,12 +3388,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250500_EX</t>
+          <t>SSEMG_R0025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SSEMG_R0025</t>
+          <t>SSEMG_STA_IS_202602250900_EX</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3558,12 +3405,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250500_LV</t>
+          <t>SSEMG_R0025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SSEMG_R0025</t>
+          <t>SSEMG_STA_IS_202602250900_LV</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3575,12 +3422,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241500_AQ</t>
+          <t>SSEMG_R0026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SSEMG_R0026</t>
+          <t>SSEMG_STA_IS_202602241100_AQ</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3592,12 +3439,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241500_NU</t>
+          <t>SSEMG_R0026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SSEMG_R0026</t>
+          <t>SSEMG_STA_IS_202602241100_NU</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3609,12 +3456,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241500_EX</t>
+          <t>SSEMG_R0026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SSEMG_R0026</t>
+          <t>SSEMG_STA_IS_202602241100_EX</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3626,12 +3473,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241500_LV</t>
+          <t>SSEMG_R0026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SSEMG_R0026</t>
+          <t>SSEMG_STA_IS_202602241100_LV</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3643,12 +3490,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602232100_AQ</t>
+          <t>SSEMG_R0027</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SSEMG_R0027</t>
+          <t>SSEMG_COA_IS_202602241900_AQ</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3660,12 +3507,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602232100_NU</t>
+          <t>SSEMG_R0027</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SSEMG_R0027</t>
+          <t>SSEMG_COA_IS_202602241900_NU</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3677,12 +3524,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602232100_EX</t>
+          <t>SSEMG_R0027</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SSEMG_R0027</t>
+          <t>SSEMG_COA_IS_202602241900_EX</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3694,12 +3541,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602232100_LV</t>
+          <t>SSEMG_R0027</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SSEMG_R0027</t>
+          <t>SSEMG_COA_IS_202602241900_LV</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3711,12 +3558,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602251300_AQ</t>
+          <t>SSEMG_R0028</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SSEMG_R0028</t>
+          <t>SSEMG_COA_IS_202602240500_AQ</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3728,12 +3575,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602251300_NU</t>
+          <t>SSEMG_R0028</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SSEMG_R0028</t>
+          <t>SSEMG_COA_IS_202602240500_NU</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3745,12 +3592,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602251300_EX</t>
+          <t>SSEMG_R0028</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SSEMG_R0028</t>
+          <t>SSEMG_COA_IS_202602240500_EX</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3762,12 +3609,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602251300_LV</t>
+          <t>SSEMG_R0028</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SSEMG_R0028</t>
+          <t>SSEMG_COA_IS_202602240500_LV</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3779,12 +3626,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241900_AQ</t>
+          <t>SSEMG_R0029</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SSEMG_R0029</t>
+          <t>SSEMG_COA_IS_202602250100_AQ</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3796,12 +3643,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241900_NU</t>
+          <t>SSEMG_R0029</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SSEMG_R0029</t>
+          <t>SSEMG_COA_IS_202602250100_NU</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3813,12 +3660,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241900_EX</t>
+          <t>SSEMG_R0029</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SSEMG_R0029</t>
+          <t>SSEMG_COA_IS_202602250100_EX</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3830,12 +3677,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241900_LV</t>
+          <t>SSEMG_R0029</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SSEMG_R0029</t>
+          <t>SSEMG_COA_IS_202602250100_LV</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3847,12 +3694,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241100_AQ</t>
+          <t>SSEMG_R0030</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SSEMG_R0030</t>
+          <t>SSEMG_COA_IS_202602241500_AQ</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3864,12 +3711,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241100_NU</t>
+          <t>SSEMG_R0030</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SSEMG_R0030</t>
+          <t>SSEMG_COA_IS_202602241500_NU</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3881,12 +3728,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241100_EX</t>
+          <t>SSEMG_R0030</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SSEMG_R0030</t>
+          <t>SSEMG_COA_IS_202602241500_EX</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3898,12 +3745,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241100_LV</t>
+          <t>SSEMG_R0030</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SSEMG_R0030</t>
+          <t>SSEMG_COA_IS_202602241500_LV</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3915,12 +3762,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240700_AQ</t>
+          <t>SSEMG_R0031</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SSEMG_R0031</t>
+          <t>SSEMG_COA_IS_202602251300_AQ</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3932,12 +3779,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240700_NU</t>
+          <t>SSEMG_R0031</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SSEMG_R0031</t>
+          <t>SSEMG_COA_IS_202602251300_NU</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3949,12 +3796,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240700_EX</t>
+          <t>SSEMG_R0031</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SSEMG_R0031</t>
+          <t>SSEMG_COA_IS_202602251300_EX</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3966,12 +3813,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240700_LV</t>
+          <t>SSEMG_R0031</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SSEMG_R0031</t>
+          <t>SSEMG_COA_IS_202602251300_LV</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3983,12 +3830,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231500_AQ</t>
+          <t>SSEMG_R0032</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SSEMG_R0032</t>
+          <t>SSEMG_COA_IS_202602240300_AQ</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4000,12 +3847,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231500_NU</t>
+          <t>SSEMG_R0032</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SSEMG_R0032</t>
+          <t>SSEMG_COA_IS_202602240300_NU</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4017,12 +3864,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231500_EX</t>
+          <t>SSEMG_R0032</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SSEMG_R0032</t>
+          <t>SSEMG_COA_IS_202602240300_EX</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4034,12 +3881,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231500_LV</t>
+          <t>SSEMG_R0032</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SSEMG_R0032</t>
+          <t>SSEMG_COA_IS_202602240300_LV</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4051,12 +3898,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602232300_AQ</t>
+          <t>SSEMG_R0033</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SSEMG_R0033</t>
+          <t>SSEMG_STA_IS_202602231900_AQ</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4068,12 +3915,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602232300_NU</t>
+          <t>SSEMG_R0033</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SSEMG_R0033</t>
+          <t>SSEMG_STA_IS_202602231900_NU</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4085,12 +3932,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602232300_EX</t>
+          <t>SSEMG_R0033</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SSEMG_R0033</t>
+          <t>SSEMG_STA_IS_202602231900_EX</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4102,12 +3949,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602232300_LV</t>
+          <t>SSEMG_R0033</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SSEMG_R0033</t>
+          <t>SSEMG_STA_IS_202602231900_LV</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4119,12 +3966,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602242100_AQ</t>
+          <t>SSEMG_R0034</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SSEMG_R0034</t>
+          <t>SSEMG_COA_IS_202602240100_AQ</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4136,12 +3983,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602242100_NU</t>
+          <t>SSEMG_R0034</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SSEMG_R0034</t>
+          <t>SSEMG_COA_IS_202602240100_NU</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4153,12 +4000,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602242100_EX</t>
+          <t>SSEMG_R0034</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SSEMG_R0034</t>
+          <t>SSEMG_COA_IS_202602240100_EX</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4170,12 +4017,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602242100_LV</t>
+          <t>SSEMG_R0034</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SSEMG_R0034</t>
+          <t>SSEMG_COA_IS_202602240100_LV</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4187,12 +4034,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602251300_AQ</t>
+          <t>SSEMG_R0035</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SSEMG_R0035</t>
+          <t>SSEMG_STA_IS_202602240100_AQ</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4204,12 +4051,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602251300_NU</t>
+          <t>SSEMG_R0035</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SSEMG_R0035</t>
+          <t>SSEMG_STA_IS_202602240100_NU</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4221,12 +4068,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602251300_EX</t>
+          <t>SSEMG_R0035</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SSEMG_R0035</t>
+          <t>SSEMG_STA_IS_202602240100_EX</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4238,12 +4085,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602251300_LV</t>
+          <t>SSEMG_R0035</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SSEMG_R0035</t>
+          <t>SSEMG_STA_IS_202602240100_LV</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4255,12 +4102,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602251100_AQ</t>
+          <t>SSEMG_R0036</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SSEMG_R0036</t>
+          <t>SSEMG_COA_IS_202602231900_AQ</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4272,12 +4119,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602251100_NU</t>
+          <t>SSEMG_R0036</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SSEMG_R0036</t>
+          <t>SSEMG_COA_IS_202602231900_NU</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4289,12 +4136,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602251100_EX</t>
+          <t>SSEMG_R0036</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SSEMG_R0036</t>
+          <t>SSEMG_COA_IS_202602231900_EX</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4306,12 +4153,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602251100_LV</t>
+          <t>SSEMG_R0036</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SSEMG_R0036</t>
+          <t>SSEMG_COA_IS_202602231900_LV</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4323,12 +4170,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250300_AQ</t>
+          <t>SSEMG_R0037</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SSEMG_R0037</t>
+          <t>SSEMG_STA_IS_202602240300_AQ</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4340,12 +4187,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250300_NU</t>
+          <t>SSEMG_R0037</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SSEMG_R0037</t>
+          <t>SSEMG_STA_IS_202602240300_NU</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4357,12 +4204,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250300_EX</t>
+          <t>SSEMG_R0037</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SSEMG_R0037</t>
+          <t>SSEMG_STA_IS_202602240300_EX</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4374,12 +4221,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250300_LV</t>
+          <t>SSEMG_R0037</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SSEMG_R0037</t>
+          <t>SSEMG_STA_IS_202602240300_LV</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4391,12 +4238,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250900_AQ</t>
+          <t>SSEMG_R0038</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SSEMG_R0038</t>
+          <t>SSEMG_COA_IS_202602250700_AQ</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4408,12 +4255,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250900_NU</t>
+          <t>SSEMG_R0038</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SSEMG_R0038</t>
+          <t>SSEMG_COA_IS_202602250700_NU</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4425,12 +4272,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250900_EX</t>
+          <t>SSEMG_R0038</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SSEMG_R0038</t>
+          <t>SSEMG_COA_IS_202602250700_EX</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4442,12 +4289,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602250900_LV</t>
+          <t>SSEMG_R0038</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SSEMG_R0038</t>
+          <t>SSEMG_COA_IS_202602250700_LV</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4459,12 +4306,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240100_AQ</t>
+          <t>SSEMG_R0039</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SSEMG_R0039</t>
+          <t>SSEMG_STA_IS_202602251100_AQ</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4476,12 +4323,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240100_NU</t>
+          <t>SSEMG_R0039</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SSEMG_R0039</t>
+          <t>SSEMG_STA_IS_202602251100_NU</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4493,12 +4340,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240100_EX</t>
+          <t>SSEMG_R0039</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SSEMG_R0039</t>
+          <t>SSEMG_STA_IS_202602251100_EX</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4510,12 +4357,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240100_LV</t>
+          <t>SSEMG_R0039</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SSEMG_R0039</t>
+          <t>SSEMG_STA_IS_202602251100_LV</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4527,12 +4374,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602242100_AQ</t>
+          <t>SSEMG_R0040</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SSEMG_R0040</t>
+          <t>SSEMG_COA_IS_202602242100_AQ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4544,12 +4391,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602242100_NU</t>
+          <t>SSEMG_R0040</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SSEMG_R0040</t>
+          <t>SSEMG_COA_IS_202602242100_NU</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4561,12 +4408,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602242100_EX</t>
+          <t>SSEMG_R0040</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SSEMG_R0040</t>
+          <t>SSEMG_COA_IS_202602242100_EX</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4578,12 +4425,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602242100_LV</t>
+          <t>SSEMG_R0040</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SSEMG_R0040</t>
+          <t>SSEMG_COA_IS_202602242100_LV</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4595,12 +4442,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240100_AQ</t>
+          <t>SSEMG_R0041</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SSEMG_R0041</t>
+          <t>SSEMG_COA_IS_202602240900_AQ</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4612,12 +4459,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240100_NU</t>
+          <t>SSEMG_R0041</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>SSEMG_R0041</t>
+          <t>SSEMG_COA_IS_202602240900_NU</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4629,12 +4476,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240100_EX</t>
+          <t>SSEMG_R0041</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SSEMG_R0041</t>
+          <t>SSEMG_COA_IS_202602240900_EX</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4646,12 +4493,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602240100_LV</t>
+          <t>SSEMG_R0041</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SSEMG_R0041</t>
+          <t>SSEMG_COA_IS_202602240900_LV</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4663,12 +4510,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602231900_AQ</t>
+          <t>SSEMG_R0042</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SSEMG_R0042</t>
+          <t>SSEMG_STA_IS_202602241900_AQ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4680,12 +4527,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602231900_NU</t>
+          <t>SSEMG_R0042</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SSEMG_R0042</t>
+          <t>SSEMG_STA_IS_202602241900_NU</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4697,12 +4544,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602231900_EX</t>
+          <t>SSEMG_R0042</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SSEMG_R0042</t>
+          <t>SSEMG_STA_IS_202602241900_EX</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4714,12 +4561,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602231900_LV</t>
+          <t>SSEMG_R0042</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SSEMG_R0042</t>
+          <t>SSEMG_STA_IS_202602241900_LV</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4731,12 +4578,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241100_AQ</t>
+          <t>SSEMG_R0043</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SSEMG_R0043</t>
+          <t>SSEMG_COA_IS_202602231700_AQ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4748,12 +4595,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241100_NU</t>
+          <t>SSEMG_R0043</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SSEMG_R0043</t>
+          <t>SSEMG_COA_IS_202602231700_NU</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4765,12 +4612,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241100_EX</t>
+          <t>SSEMG_R0043</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>SSEMG_R0043</t>
+          <t>SSEMG_COA_IS_202602231700_EX</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4782,12 +4629,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SSEMG_COA_IS_202602241100_LV</t>
+          <t>SSEMG_R0043</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>SSEMG_R0043</t>
+          <t>SSEMG_COA_IS_202602231700_LV</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4799,12 +4646,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602242300_AQ</t>
+          <t>SSEMG_R0044</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SSEMG_R0044</t>
+          <t>SSEMG_COA_IS_202602250300_AQ</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4816,12 +4663,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602242300_NU</t>
+          <t>SSEMG_R0044</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SSEMG_R0044</t>
+          <t>SSEMG_COA_IS_202602250300_NU</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4833,12 +4680,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602242300_EX</t>
+          <t>SSEMG_R0044</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>SSEMG_R0044</t>
+          <t>SSEMG_COA_IS_202602250300_EX</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4850,12 +4697,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602242300_LV</t>
+          <t>SSEMG_R0044</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SSEMG_R0044</t>
+          <t>SSEMG_COA_IS_202602250300_LV</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4867,12 +4714,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240500_AQ</t>
+          <t>SSEMG_R0045</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SSEMG_R0045</t>
+          <t>SSEMG_STA_IS_202602241300_AQ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4884,12 +4731,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240500_NU</t>
+          <t>SSEMG_R0045</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SSEMG_R0045</t>
+          <t>SSEMG_STA_IS_202602241300_NU</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4901,12 +4748,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240500_EX</t>
+          <t>SSEMG_R0045</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SSEMG_R0045</t>
+          <t>SSEMG_STA_IS_202602241300_EX</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4918,12 +4765,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602240500_LV</t>
+          <t>SSEMG_R0045</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SSEMG_R0045</t>
+          <t>SSEMG_STA_IS_202602241300_LV</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4935,12 +4782,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250100_AQ</t>
+          <t>SSEMG_R0046</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SSEMG_R0046</t>
+          <t>SSEMG_STA_IS_202602250300_AQ</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4952,12 +4799,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250100_NU</t>
+          <t>SSEMG_R0046</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SSEMG_R0046</t>
+          <t>SSEMG_STA_IS_202602250300_NU</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4969,12 +4816,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250100_EX</t>
+          <t>SSEMG_R0046</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>SSEMG_R0046</t>
+          <t>SSEMG_STA_IS_202602250300_EX</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4986,12 +4833,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602250100_LV</t>
+          <t>SSEMG_R0046</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SSEMG_R0046</t>
+          <t>SSEMG_STA_IS_202602250300_LV</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5003,12 +4850,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231900_AQ</t>
+          <t>SSEMG_R0047</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SSEMG_R0047</t>
+          <t>SSEMG_STA_IS_202602232300_AQ</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5020,12 +4867,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231900_NU</t>
+          <t>SSEMG_R0047</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SSEMG_R0047</t>
+          <t>SSEMG_STA_IS_202602232300_NU</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5037,12 +4884,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231900_EX</t>
+          <t>SSEMG_R0047</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SSEMG_R0047</t>
+          <t>SSEMG_STA_IS_202602232300_EX</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5054,12 +4901,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602231900_LV</t>
+          <t>SSEMG_R0047</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SSEMG_R0047</t>
+          <t>SSEMG_STA_IS_202602232300_LV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5071,12 +4918,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241500_AQ</t>
+          <t>SSEMG_R0048</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SSEMG_R0048</t>
+          <t>SSEMG_COA_IS_202602251500_AQ</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5088,12 +4935,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241500_NU</t>
+          <t>SSEMG_R0048</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SSEMG_R0048</t>
+          <t>SSEMG_COA_IS_202602251500_NU</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5105,12 +4952,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241500_EX</t>
+          <t>SSEMG_R0048</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SSEMG_R0048</t>
+          <t>SSEMG_COA_IS_202602251500_EX</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5122,12 +4969,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SSEMG_STA_IS_202602241500_LV</t>
+          <t>SSEMG_R0048</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>SSEMG_R0048</t>
+          <t>SSEMG_COA_IS_202602251500_LV</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5145,9 +4992,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="20.7109375" style="2" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
@@ -5157,7 +5001,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>time_PST</t>
+          <t>datetime_PST</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -5187,8 +5031,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B2" s="2">
-        <v>46076.95833333333</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>202602231500</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5201,7 +5047,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -5213,8 +5059,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B3" s="2">
-        <v>46077.04166666667</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>202602231700</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -5227,7 +5075,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -5239,8 +5087,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B4" s="2">
-        <v>46077.125</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>202602231900</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -5253,7 +5103,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -5265,8 +5115,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B5" s="2">
-        <v>46077.20833333333</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>202602232100</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5279,7 +5131,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -5291,8 +5143,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B6" s="2">
-        <v>46077.29166666667</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>202602232300</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -5305,7 +5159,7 @@
         </is>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5317,8 +5171,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B7" s="2">
-        <v>46077.375</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>202602240100</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -5331,7 +5187,7 @@
         </is>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -5343,8 +5199,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B8" s="2">
-        <v>46077.45833333333</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>202602240300</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -5357,7 +5215,7 @@
         </is>
       </c>
       <c r="E8">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -5369,8 +5227,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B9" s="2">
-        <v>46077.54166666667</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>202602240500</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -5383,7 +5243,7 @@
         </is>
       </c>
       <c r="E9">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -5395,8 +5255,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B10" s="2">
-        <v>46077.625</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>202602240700</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -5409,7 +5271,7 @@
         </is>
       </c>
       <c r="E10">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F10">
         <v>9</v>
@@ -5421,8 +5283,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B11" s="2">
-        <v>46077.70833333333</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>202602240900</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -5435,7 +5299,7 @@
         </is>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -5447,8 +5311,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B12" s="2">
-        <v>46077.79166666667</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>202602241100</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -5461,7 +5327,7 @@
         </is>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F12">
         <v>11</v>
@@ -5473,8 +5339,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B13" s="2">
-        <v>46077.875</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>202602241300</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -5487,7 +5355,7 @@
         </is>
       </c>
       <c r="E13">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -5499,8 +5367,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <v>46077.95833333333</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>202602241500</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -5513,7 +5383,7 @@
         </is>
       </c>
       <c r="E14">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F14">
         <v>13</v>
@@ -5525,8 +5395,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B15" s="2">
-        <v>46078.04166666667</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>202602241700</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -5539,7 +5411,7 @@
         </is>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F15">
         <v>14</v>
@@ -5551,8 +5423,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B16" s="2">
-        <v>46078.125</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>202602241900</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -5565,7 +5439,7 @@
         </is>
       </c>
       <c r="E16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F16">
         <v>15</v>
@@ -5577,8 +5451,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B17" s="2">
-        <v>46078.20833333333</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>202602242100</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -5591,7 +5467,7 @@
         </is>
       </c>
       <c r="E17">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F17">
         <v>16</v>
@@ -5603,8 +5479,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <v>46078.29166666667</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>202602242300</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -5617,7 +5495,7 @@
         </is>
       </c>
       <c r="E18">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F18">
         <v>17</v>
@@ -5629,8 +5507,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B19" s="2">
-        <v>46078.375</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>202602250100</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -5643,7 +5523,7 @@
         </is>
       </c>
       <c r="E19">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="F19">
         <v>18</v>
@@ -5655,8 +5535,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B20" s="2">
-        <v>46078.45833333333</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>202602250300</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -5669,7 +5551,7 @@
         </is>
       </c>
       <c r="E20">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F20">
         <v>19</v>
@@ -5681,8 +5563,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B21" s="2">
-        <v>46078.54166666667</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>202602250500</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -5695,7 +5579,7 @@
         </is>
       </c>
       <c r="E21">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F21">
         <v>20</v>
@@ -5707,8 +5591,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B22" s="2">
-        <v>46078.625</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>202602250700</t>
+        </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -5721,7 +5607,7 @@
         </is>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F22">
         <v>21</v>
@@ -5733,8 +5619,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B23" s="2">
-        <v>46078.70833333333</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>202602250900</t>
+        </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -5747,7 +5635,7 @@
         </is>
       </c>
       <c r="E23">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F23">
         <v>22</v>
@@ -5759,8 +5647,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B24" s="2">
-        <v>46078.79166666667</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>202602251100</t>
+        </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -5773,7 +5663,7 @@
         </is>
       </c>
       <c r="E24">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F24">
         <v>23</v>
@@ -5785,8 +5675,10 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="B25" s="2">
-        <v>46078.875</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>202602251300</t>
+        </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -5799,7 +5691,7 @@
         </is>
       </c>
       <c r="E25">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="F25">
         <v>24</v>
@@ -5811,8 +5703,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B26" s="2">
-        <v>46077.04166666667</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>202602231700</t>
+        </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -5825,7 +5719,7 @@
         </is>
       </c>
       <c r="E26">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -5837,8 +5731,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B27" s="2">
-        <v>46077.125</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>202602231900</t>
+        </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -5851,7 +5747,7 @@
         </is>
       </c>
       <c r="E27">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F27">
         <v>2</v>
@@ -5863,8 +5759,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B28" s="2">
-        <v>46077.20833333333</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>202602232100</t>
+        </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -5877,7 +5775,7 @@
         </is>
       </c>
       <c r="E28">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F28">
         <v>3</v>
@@ -5889,8 +5787,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B29" s="2">
-        <v>46077.29166666667</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>202602232300</t>
+        </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -5903,7 +5803,7 @@
         </is>
       </c>
       <c r="E29">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="F29">
         <v>4</v>
@@ -5915,8 +5815,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B30" s="2">
-        <v>46077.375</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>202602240100</t>
+        </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -5929,7 +5831,7 @@
         </is>
       </c>
       <c r="E30">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F30">
         <v>5</v>
@@ -5941,8 +5843,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B31" s="2">
-        <v>46077.45833333333</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>202602240300</t>
+        </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -5955,7 +5859,7 @@
         </is>
       </c>
       <c r="E31">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F31">
         <v>6</v>
@@ -5967,8 +5871,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B32" s="2">
-        <v>46077.54166666667</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>202602240500</t>
+        </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5981,7 +5887,7 @@
         </is>
       </c>
       <c r="E32">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="F32">
         <v>7</v>
@@ -5993,8 +5899,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B33" s="2">
-        <v>46077.625</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>202602240700</t>
+        </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -6007,7 +5915,7 @@
         </is>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F33">
         <v>8</v>
@@ -6019,8 +5927,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B34" s="2">
-        <v>46077.70833333333</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>202602240900</t>
+        </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -6033,7 +5943,7 @@
         </is>
       </c>
       <c r="E34">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F34">
         <v>9</v>
@@ -6045,8 +5955,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B35" s="2">
-        <v>46077.79166666667</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>202602241100</t>
+        </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -6059,7 +5971,7 @@
         </is>
       </c>
       <c r="E35">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="F35">
         <v>10</v>
@@ -6071,8 +5983,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B36" s="2">
-        <v>46077.875</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>202602241300</t>
+        </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -6085,7 +5999,7 @@
         </is>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F36">
         <v>11</v>
@@ -6097,8 +6011,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B37" s="2">
-        <v>46077.95833333333</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>202602241500</t>
+        </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -6111,7 +6027,7 @@
         </is>
       </c>
       <c r="E37">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="F37">
         <v>12</v>
@@ -6123,8 +6039,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B38" s="2">
-        <v>46078.04166666667</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>202602241700</t>
+        </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -6137,7 +6055,7 @@
         </is>
       </c>
       <c r="E38">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F38">
         <v>13</v>
@@ -6149,8 +6067,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B39" s="2">
-        <v>46078.125</v>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>202602241900</t>
+        </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -6163,7 +6083,7 @@
         </is>
       </c>
       <c r="E39">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F39">
         <v>14</v>
@@ -6175,8 +6095,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B40" s="2">
-        <v>46078.20833333333</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>202602242100</t>
+        </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6189,7 +6111,7 @@
         </is>
       </c>
       <c r="E40">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F40">
         <v>15</v>
@@ -6201,8 +6123,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B41" s="2">
-        <v>46078.29166666667</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>202602242300</t>
+        </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6215,7 +6139,7 @@
         </is>
       </c>
       <c r="E41">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F41">
         <v>16</v>
@@ -6227,8 +6151,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B42" s="2">
-        <v>46078.375</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>202602250100</t>
+        </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6241,7 +6167,7 @@
         </is>
       </c>
       <c r="E42">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="F42">
         <v>17</v>
@@ -6253,8 +6179,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B43" s="2">
-        <v>46078.45833333333</v>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>202602250300</t>
+        </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6267,7 +6195,7 @@
         </is>
       </c>
       <c r="E43">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F43">
         <v>18</v>
@@ -6279,8 +6207,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B44" s="2">
-        <v>46078.54166666667</v>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>202602250500</t>
+        </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6293,7 +6223,7 @@
         </is>
       </c>
       <c r="E44">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F44">
         <v>19</v>
@@ -6305,8 +6235,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B45" s="2">
-        <v>46078.625</v>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>202602250700</t>
+        </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6319,7 +6251,7 @@
         </is>
       </c>
       <c r="E45">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="F45">
         <v>20</v>
@@ -6331,8 +6263,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B46" s="2">
-        <v>46078.70833333333</v>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>202602250900</t>
+        </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6345,7 +6279,7 @@
         </is>
       </c>
       <c r="E46">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F46">
         <v>21</v>
@@ -6357,8 +6291,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B47" s="2">
-        <v>46078.79166666667</v>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>202602251100</t>
+        </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6371,7 +6307,7 @@
         </is>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F47">
         <v>22</v>
@@ -6383,8 +6319,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B48" s="2">
-        <v>46078.875</v>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>202602251300</t>
+        </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6397,7 +6335,7 @@
         </is>
       </c>
       <c r="E48">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F48">
         <v>23</v>
@@ -6409,8 +6347,10 @@
           <t>COA</t>
         </is>
       </c>
-      <c r="B49" s="2">
-        <v>46078.95833333333</v>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>202602251500</t>
+        </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6423,7 +6363,7 @@
         </is>
       </c>
       <c r="E49">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="F49">
         <v>24</v>
